--- a/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
+++ b/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5358" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5382" uniqueCount="665">
   <si>
     <t>Result</t>
   </si>
@@ -2045,6 +2045,24 @@
   </si>
   <si>
     <t>Mon Nov 17 19:38:12 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 19:49:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 19:51:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 19:54:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 19:57:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:09:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:10:44 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -6317,7 +6335,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>587</v>
+        <v>659</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6407,7 +6425,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>588</v>
+        <v>660</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7510,7 +7528,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7594,10 +7612,10 @@
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>621</v>
+        <v>662</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -8636,7 +8654,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>609</v>
+        <v>663</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8732,7 +8750,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>610</v>
+        <v>664</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>

--- a/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
+++ b/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5382" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6186" uniqueCount="866">
   <si>
     <t>Result</t>
   </si>
@@ -2063,6 +2063,609 @@
   </si>
   <si>
     <t>Wed Jan 21 20:10:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 22:36:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 22:37:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 22:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 22:59:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 23:01:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 23:23:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 23:25:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 23:50:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 23:52:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 23:55:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 23:57:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:01:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:06:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:08:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:10:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:12:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:41:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:42:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:43:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:44:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:45:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:46:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:47:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:48:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:56:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:56:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:57:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:58:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:00:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:01:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:02:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:02:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:03:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:04:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:05:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:06:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:07:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:08:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:10:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:19:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:20:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:21:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:22:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:24:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:25:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:26:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:29:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:29:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:30:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:32:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:33:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:34:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:36:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:37:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:38:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:39:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:40:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:42:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:43:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:45:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:47:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:48:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:49:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:50:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:53:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:54:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:55:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:33:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:35:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:37:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:38:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:40:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:42:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:43:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:44:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:45:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:47:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:48:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:48:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:49:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:52:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:52:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:53:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:54:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:56:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:58:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:59:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:00:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:02:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:03:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:05:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:10:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:12:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:43:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:44:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:47:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:48:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:50:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:51:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:54:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:55:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 06:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 07:01:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 07:02:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:36:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:37:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:38:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:39:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:40:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:41:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:42:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:51:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:52:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:53:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:53:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:54:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:55:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:56:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:57:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:58:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 08:59:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:00:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:02:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:03:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:04:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:05:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:14:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:16:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:17:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:18:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:19:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:20:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:22:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:24:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:24:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:25:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:27:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:28:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:29:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:30:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:31:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:34:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:35:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:36:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:37:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:38:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:40:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:41:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:42:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:43:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:45:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:47:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:49:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 09:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:28:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:29:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:30:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:31:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:32:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:33:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:34:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:35:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:37:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:38:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:39:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:41:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:41:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:44:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:44:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:47:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:48:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:49:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:51:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:52:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:53:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:55:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:56:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 10:57:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 20:37:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 20:40:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 20:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 21:23:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 21:25:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 23:54:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 23:56:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 00:15:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 00:28:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2527,10 +3130,10 @@
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>603</v>
+        <v>809</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -2617,7 +3220,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>604</v>
+        <v>810</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -3213,7 +3816,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>581</v>
+        <v>787</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -3299,7 +3902,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>582</v>
+        <v>788</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -3693,7 +4296,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>573</v>
+        <v>779</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -3782,7 +4385,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>574</v>
+        <v>780</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -3973,7 +4576,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>589</v>
+        <v>795</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4063,7 +4666,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>590</v>
+        <v>796</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4258,7 +4861,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>585</v>
+        <v>791</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4353,7 +4956,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>586</v>
+        <v>792</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4562,7 +5165,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>593</v>
+        <v>799</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4661,7 +5264,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>594</v>
+        <v>800</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4859,7 +5462,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>571</v>
+        <v>777</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -4948,7 +5551,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>572</v>
+        <v>778</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -5142,10 +5745,10 @@
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>575</v>
+        <v>781</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5243,7 +5846,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>576</v>
+        <v>782</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5460,7 +6063,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>607</v>
+        <v>813</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5556,7 +6159,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>608</v>
+        <v>814</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5760,7 +6363,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>577</v>
+        <v>783</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5858,7 +6461,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>578</v>
+        <v>784</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6058,7 +6661,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>579</v>
+        <v>785</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6147,7 +6750,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>580</v>
+        <v>786</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -6335,7 +6938,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>659</v>
+        <v>793</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6425,7 +7028,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>660</v>
+        <v>794</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -6620,7 +7223,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>583</v>
+        <v>789</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6715,7 +7318,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>584</v>
+        <v>790</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6925,7 +7528,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>591</v>
+        <v>797</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7025,7 +7628,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>592</v>
+        <v>798</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7232,10 +7835,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>624</v>
+        <v>830</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7329,10 +7932,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>625</v>
+        <v>831</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7525,10 +8128,10 @@
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>661</v>
+        <v>826</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7612,10 +8215,10 @@
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>662</v>
+        <v>827</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7810,10 +8413,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>622</v>
+        <v>828</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7907,10 +8510,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>623</v>
+        <v>829</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8109,7 +8712,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>618</v>
+        <v>859</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8197,7 +8800,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>619</v>
+        <v>858</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8384,7 +8987,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>722</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8465,7 +9068,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>611</v>
+        <v>817</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8654,7 +9257,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>663</v>
+        <v>815</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8750,7 +9353,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>664</v>
+        <v>816</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8942,7 +9545,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>612</v>
+        <v>818</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -9022,7 +9625,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>613</v>
+        <v>819</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -9204,10 +9807,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>614</v>
+        <v>820</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9296,7 +9899,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>615</v>
+        <v>821</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9490,7 +10093,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>616</v>
+        <v>860</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9579,7 +10182,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>617</v>
+        <v>861</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9764,7 +10367,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>636</v>
+        <v>841</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9846,7 +10449,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>637</v>
+        <v>842</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10021,10 +10624,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>634</v>
+        <v>839</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -10106,7 +10709,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>635</v>
+        <v>840</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -10290,10 +10893,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>638</v>
+        <v>843</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10384,7 +10987,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>639</v>
+        <v>844</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10568,10 +11171,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>656</v>
+        <v>849</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10653,7 +11256,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>655</v>
+        <v>850</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10828,10 +11431,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>642</v>
+        <v>847</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -10913,7 +11516,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>643</v>
+        <v>848</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -11097,10 +11700,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>648</v>
+        <v>853</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11191,7 +11794,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>649</v>
+        <v>854</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11384,10 +11987,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>652</v>
+        <v>851</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11478,7 +12081,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>653</v>
+        <v>852</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11668,10 +12271,10 @@
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>605</v>
+        <v>811</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -11758,7 +12361,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>606</v>
+        <v>812</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -11944,7 +12547,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>628</v>
+        <v>834</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12204,7 +12807,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>657</v>
+        <v>832</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -12286,7 +12889,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>658</v>
+        <v>833</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -12473,7 +13076,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>630</v>
+        <v>835</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12564,7 +13167,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>631</v>
+        <v>836</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -12757,10 +13360,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>632</v>
+        <v>837</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12851,7 +13454,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>633</v>
+        <v>838</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13044,10 +13647,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>640</v>
+        <v>845</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13138,7 +13741,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>641</v>
+        <v>846</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13334,7 +13937,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>595</v>
+        <v>864</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13414,7 +14017,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>596</v>
+        <v>863</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13590,7 +14193,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>597</v>
+        <v>803</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -13670,7 +14273,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>598</v>
+        <v>804</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -13855,7 +14458,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>599</v>
+        <v>865</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13944,7 +14547,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>600</v>
+        <v>806</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14138,7 +14741,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>601</v>
+        <v>807</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14227,7 +14830,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>602</v>
+        <v>808</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14412,7 +15015,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>650</v>
+        <v>855</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
@@ -14468,7 +15071,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>651</v>
+        <v>856</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>75</v>

--- a/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
+++ b/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6186" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6666" uniqueCount="986">
   <si>
     <t>Result</t>
   </si>
@@ -2666,6 +2666,366 @@
   </si>
   <si>
     <t>Wed Mar 11 00:28:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:16:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:18:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:20:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:22:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:23:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:24:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:25:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:28:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:45:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:46:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:47:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:48:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:49:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:50:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:36:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:37:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:38:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:39:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:41:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:46:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:48:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:56:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:57:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:58:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:00:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:01:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:02:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:02:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:03:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:04:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:06:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:07:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:09:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:10:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:11:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:20:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:22:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:23:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:24:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:26:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:27:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:28:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:30:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:31:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:32:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:33:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:34:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:35:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:36:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:37:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:39:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:41:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:42:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:43:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:44:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:47:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:49:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:50:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:51:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:52:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:53:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:54:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:56:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:57:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:36:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:37:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:38:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:40:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:41:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:43:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:44:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:45:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:46:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:47:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:48:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:49:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:50:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:51:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:53:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:56:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:58:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:59:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:00:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:01:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:02:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:03:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:04:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:05:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:06:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:07:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:07:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 03:08:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:39:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:41:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:42:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:15:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:18:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:19:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:20:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:22:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:23:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:24:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:26:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:27:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:28:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:29:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:30:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:31:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:32:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:33:40 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3133,7 +3493,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>809</v>
+        <v>978</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -3220,7 +3580,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>810</v>
+        <v>979</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -3403,7 +3763,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>961</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>78</v>
@@ -3457,7 +3817,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>962</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>78</v>
@@ -3610,7 +3970,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>967</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>79</v>
@@ -3665,7 +4025,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>968</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
@@ -3816,7 +4176,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>787</v>
+        <v>891</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -3902,7 +4262,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>788</v>
+        <v>892</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4087,7 +4447,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>969</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>79</v>
@@ -4142,7 +4502,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>970</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
@@ -4296,7 +4656,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>779</v>
+        <v>883</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4385,7 +4745,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>780</v>
+        <v>884</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4576,7 +4936,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>795</v>
+        <v>899</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4666,7 +5026,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>796</v>
+        <v>900</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4861,7 +5221,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>791</v>
+        <v>895</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4956,7 +5316,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>792</v>
+        <v>896</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5165,7 +5525,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>799</v>
+        <v>903</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5264,7 +5624,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>800</v>
+        <v>904</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5462,7 +5822,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>777</v>
+        <v>881</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -5551,7 +5911,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>778</v>
+        <v>882</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -5748,7 +6108,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>781</v>
+        <v>885</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5846,7 +6206,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>782</v>
+        <v>886</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6063,7 +6423,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>813</v>
+        <v>982</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6159,7 +6519,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>814</v>
+        <v>983</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6363,7 +6723,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>783</v>
+        <v>887</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6461,7 +6821,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>784</v>
+        <v>888</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6661,7 +7021,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>785</v>
+        <v>889</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6750,7 +7110,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>786</v>
+        <v>890</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -6938,7 +7298,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>793</v>
+        <v>897</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7028,7 +7388,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>794</v>
+        <v>898</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7223,7 +7583,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>789</v>
+        <v>893</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7318,7 +7678,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>790</v>
+        <v>894</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7528,7 +7888,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>797</v>
+        <v>901</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7628,7 +7988,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>798</v>
+        <v>902</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7835,10 +8195,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>830</v>
+        <v>934</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7932,10 +8292,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>831</v>
+        <v>935</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8128,10 +8488,10 @@
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>826</v>
+        <v>930</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -8215,10 +8575,10 @@
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>827</v>
+        <v>931</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -8413,10 +8773,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>828</v>
+        <v>932</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8510,10 +8870,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>829</v>
+        <v>933</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8712,7 +9072,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>859</v>
+        <v>928</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8800,7 +9160,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>858</v>
+        <v>929</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8984,10 +9344,10 @@
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>722</v>
+        <v>920</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9068,7 +9428,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>817</v>
+        <v>921</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9257,7 +9617,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>815</v>
+        <v>984</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9353,7 +9713,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>816</v>
+        <v>985</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9542,10 +9902,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>818</v>
+        <v>922</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -9625,7 +9985,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>819</v>
+        <v>923</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -9810,7 +10170,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>820</v>
+        <v>924</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9899,7 +10259,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>821</v>
+        <v>925</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10093,7 +10453,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>860</v>
+        <v>926</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10182,7 +10542,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>861</v>
+        <v>927</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10367,7 +10727,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>841</v>
+        <v>945</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10449,7 +10809,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>842</v>
+        <v>946</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10627,7 +10987,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>839</v>
+        <v>943</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -10709,7 +11069,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>840</v>
+        <v>944</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -10893,10 +11253,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>843</v>
+        <v>947</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10987,7 +11347,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>844</v>
+        <v>948</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11174,7 +11534,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>849</v>
+        <v>953</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11256,7 +11616,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>850</v>
+        <v>954</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11431,10 +11791,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>847</v>
+        <v>951</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -11516,7 +11876,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>848</v>
+        <v>952</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -11700,10 +12060,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>853</v>
+        <v>957</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11794,7 +12154,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>854</v>
+        <v>958</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11987,10 +12347,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>851</v>
+        <v>955</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12081,7 +12441,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>852</v>
+        <v>956</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -12271,10 +12631,10 @@
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>811</v>
+        <v>980</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -12361,7 +12721,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>812</v>
+        <v>981</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -12544,10 +12904,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>834</v>
+        <v>938</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12807,7 +13167,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>832</v>
+        <v>936</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -12889,7 +13249,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>833</v>
+        <v>937</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -13073,10 +13433,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>835</v>
+        <v>939</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13167,7 +13527,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>836</v>
+        <v>940</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13363,7 +13723,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>837</v>
+        <v>941</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13454,7 +13814,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>838</v>
+        <v>942</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13647,10 +14007,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>845</v>
+        <v>949</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13741,7 +14101,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>846</v>
+        <v>950</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13934,10 +14294,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>864</v>
+        <v>971</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14193,7 +14553,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>803</v>
+        <v>972</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -14273,7 +14633,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>804</v>
+        <v>973</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -14455,10 +14815,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>865</v>
+        <v>974</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14547,7 +14907,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>806</v>
+        <v>975</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14738,10 +15098,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>807</v>
+        <v>976</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14830,7 +15190,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -15015,7 +15375,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>855</v>
+        <v>959</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
@@ -15071,7 +15431,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>856</v>
+        <v>960</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>75</v>

--- a/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
+++ b/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6666" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1094">
   <si>
     <t>Result</t>
   </si>
@@ -3026,6 +3026,330 @@
   </si>
   <si>
     <t>Thu May 07 22:33:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:05:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:06:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:07:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:08:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:10:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:11:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:12:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:13:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:22:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:22:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:23:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:24:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:25:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:26:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:27:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:28:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:29:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:30:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:32:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:33:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:34:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:43:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:44:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:45:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:46:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:48:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:51:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:52:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:53:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:54:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:55:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:56:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:57:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:58:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:59:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:00:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:01:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:03:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:05:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:06:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:07:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:09:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:10:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:11:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:12:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:13:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:14:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:16:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:17:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:53:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:54:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:55:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:57:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:58:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:59:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:00:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:02:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:02:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:03:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:04:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:05:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:06:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:07:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:08:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:08:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:10:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:11:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:13:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:14:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:15:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:16:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:17:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:18:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:19:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:20:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:22:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 02:22:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:44:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:45:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:46:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:47:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:48:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:50:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:13:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:14:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:16:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:17:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:19:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:20:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:22:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:23:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:24:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:25:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:26:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:27:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:28:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:29:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:30:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 23 20:28:23 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3493,7 +3817,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>978</v>
+        <v>1085</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -3580,7 +3904,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>979</v>
+        <v>1086</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -3763,7 +4087,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>961</v>
+        <v>1072</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>78</v>
@@ -3817,7 +4141,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>962</v>
+        <v>1073</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>78</v>
@@ -3970,7 +4294,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>967</v>
+        <v>1074</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>79</v>
@@ -4025,7 +4349,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
@@ -4176,7 +4500,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>891</v>
+        <v>996</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4262,7 +4586,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>892</v>
+        <v>997</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4447,7 +4771,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>969</v>
+        <v>1076</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>79</v>
@@ -4502,7 +4826,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>970</v>
+        <v>1077</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
@@ -4656,7 +4980,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>883</v>
+        <v>988</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4745,7 +5069,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>884</v>
+        <v>989</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4936,7 +5260,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>899</v>
+        <v>1004</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5026,7 +5350,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>900</v>
+        <v>1005</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5221,7 +5545,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>895</v>
+        <v>1000</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5316,7 +5640,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>896</v>
+        <v>1001</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5525,7 +5849,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>903</v>
+        <v>1008</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5624,7 +5948,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>904</v>
+        <v>1009</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5822,7 +6146,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>881</v>
+        <v>986</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -5911,7 +6235,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>882</v>
+        <v>987</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -6108,7 +6432,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>885</v>
+        <v>990</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6206,7 +6530,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6423,7 +6747,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>982</v>
+        <v>1089</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6519,7 +6843,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>983</v>
+        <v>1090</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6723,7 +7047,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>887</v>
+        <v>992</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6821,7 +7145,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>888</v>
+        <v>993</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7021,7 +7345,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>889</v>
+        <v>994</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7110,7 +7434,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>890</v>
+        <v>995</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7298,7 +7622,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>897</v>
+        <v>1002</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7388,7 +7712,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>898</v>
+        <v>1003</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7583,7 +7907,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>893</v>
+        <v>998</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7678,7 +8002,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>894</v>
+        <v>999</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7888,7 +8212,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>901</v>
+        <v>1006</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7988,7 +8312,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>902</v>
+        <v>1007</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8198,7 +8522,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>934</v>
+        <v>1039</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8295,7 +8619,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>935</v>
+        <v>1040</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8491,7 +8815,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>930</v>
+        <v>1035</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -8578,7 +8902,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>931</v>
+        <v>1036</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -8776,7 +9100,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>932</v>
+        <v>1037</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8873,7 +9197,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>933</v>
+        <v>1038</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9072,7 +9396,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>928</v>
+        <v>1033</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9160,7 +9484,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>929</v>
+        <v>1034</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9347,7 +9671,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>920</v>
+        <v>1025</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9428,7 +9752,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>921</v>
+        <v>1026</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9617,7 +9941,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>984</v>
+        <v>1091</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9713,7 +10037,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>985</v>
+        <v>1092</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9905,7 +10229,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>922</v>
+        <v>1027</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -9985,7 +10309,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>923</v>
+        <v>1028</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -10170,7 +10494,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>924</v>
+        <v>1029</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10259,7 +10583,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>925</v>
+        <v>1030</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10453,7 +10777,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>926</v>
+        <v>1031</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10542,7 +10866,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>927</v>
+        <v>1032</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10727,7 +11051,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>945</v>
+        <v>1050</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10809,7 +11133,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>946</v>
+        <v>1051</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10987,7 +11311,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>943</v>
+        <v>1048</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -11069,7 +11393,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>944</v>
+        <v>1049</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -11256,7 +11580,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>947</v>
+        <v>1052</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11347,7 +11671,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>948</v>
+        <v>1053</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11534,7 +11858,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>953</v>
+        <v>1058</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11616,7 +11940,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>954</v>
+        <v>1059</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11794,7 +12118,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>951</v>
+        <v>1056</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -11876,7 +12200,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>952</v>
+        <v>1057</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -12063,7 +12387,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>957</v>
+        <v>1062</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12154,7 +12478,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>958</v>
+        <v>1063</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -12350,7 +12674,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>955</v>
+        <v>1060</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12441,7 +12765,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>956</v>
+        <v>1061</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -12634,7 +12958,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>980</v>
+        <v>1087</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -12721,7 +13045,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>981</v>
+        <v>1088</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -12907,7 +13231,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>938</v>
+        <v>1043</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13167,7 +13491,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>936</v>
+        <v>1041</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -13249,7 +13573,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>937</v>
+        <v>1042</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -13436,7 +13760,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>939</v>
+        <v>1044</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13527,7 +13851,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>940</v>
+        <v>1045</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13723,7 +14047,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>941</v>
+        <v>1046</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13814,7 +14138,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>942</v>
+        <v>1047</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14010,7 +14334,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>949</v>
+        <v>1054</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14101,7 +14425,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>950</v>
+        <v>1055</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14294,10 +14618,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>971</v>
+        <v>1093</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14553,7 +14877,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>972</v>
+        <v>1079</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -14633,7 +14957,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>973</v>
+        <v>1080</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -14818,7 +15142,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>974</v>
+        <v>1081</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14907,7 +15231,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>975</v>
+        <v>1082</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -15101,7 +15425,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>976</v>
+        <v>1083</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -15190,7 +15514,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>977</v>
+        <v>1084</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -15375,7 +15699,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>959</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
@@ -15431,7 +15755,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>960</v>
+        <v>1065</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>75</v>

--- a/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
+++ b/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7100" uniqueCount="1095">
   <si>
     <t>Result</t>
   </si>
@@ -3350,6 +3350,9 @@
   </si>
   <si>
     <t>Tue Jun 23 20:28:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 20:59:07 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3716,7 +3719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480F8651-F3AC-4535-B367-EFECB2CBCC7D}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="19.0" collapsed="true"/>
@@ -3813,10 +3816,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1085</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3900,10 +3903,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1086</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3993,7 +3996,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82F529ED-3A89-4F8F-BD36-459852A5DF83}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -4083,10 +4086,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1072</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -4137,10 +4140,10 @@
       <c r="AB2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1073</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4197,7 +4200,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA264D1-2E50-4CB9-BFEE-8C623610CE21}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -4290,10 +4293,10 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1074</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -4345,10 +4348,10 @@
       <c r="AC2" s="1"/>
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1075</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4406,7 +4409,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460D88B6-A386-4846-BE51-48B1BF32CF9B}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -4496,10 +4499,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>996</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -4582,10 +4585,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>997</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4674,7 +4677,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66FEF4E2-BFBF-46DF-A493-61D536E6B905}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -4767,10 +4770,10 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1076</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -4822,10 +4825,10 @@
       <c r="AC2" s="1"/>
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1077</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -4883,7 +4886,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A45949-68BF-404E-8F7F-FB2E9E2F425C}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -4976,10 +4979,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>988</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5065,10 +5068,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>989</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5160,7 +5163,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4B946A-2C4C-46EF-93A1-2FF7963F4F9C}">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -5256,10 +5259,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1004</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5346,10 +5349,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1005</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5442,7 +5445,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB1C7FA-E6AE-425E-93E9-7344162BF220}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -5541,10 +5544,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1000</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5636,10 +5639,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1001</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5737,7 +5740,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F90F0E-2E15-46C5-95C8-91EEE2324B31}">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="29.0" collapsed="true"/>
@@ -5845,10 +5848,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1008</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5944,10 +5947,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1009</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6049,7 +6052,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D305C12C-5443-4486-B7D9-3C403F6F0EF8}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -6142,10 +6145,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>986</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -6231,10 +6234,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>987</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6326,7 +6329,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E446BF9-B02F-4740-AE83-9C5B060028BD}">
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:32" x14ac:dyDescent="0.3">
@@ -6428,10 +6431,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>990</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -6526,10 +6529,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>991</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6630,7 +6633,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C90F22-FE25-4600-AD2E-915F2F742F43}">
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" style="2" width="8.6640625" collapsed="true"/>
@@ -6743,10 +6746,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="2">
         <v>1089</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -6839,10 +6842,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="2">
         <v>1090</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6941,7 +6944,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6083FB1-02F1-48D6-92EE-3F1FBC7D79B0}">
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:32" x14ac:dyDescent="0.3">
@@ -7043,10 +7046,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>992</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -7141,10 +7144,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>993</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -7245,7 +7248,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF9C0F3-0DA7-44CD-B9A8-E552BD6DF9FF}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="23.33203125" collapsed="true"/>
@@ -7341,10 +7344,10 @@
       <c r="AE1" s="1"/>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>994</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -7430,10 +7433,10 @@
       <c r="AE2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>995</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -7522,7 +7525,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F02A9F4-7828-4F92-A71A-133EDBD34118}">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -7618,10 +7621,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1002</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -7708,10 +7711,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1003</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -7804,7 +7807,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6314CBCE-7A5E-4A0C-AF29-C3F1F0871FFF}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -7903,10 +7906,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>998</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -7998,10 +8001,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>999</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -8099,7 +8102,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9259111-57D2-4ED8-A106-9387F81FA5DC}">
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="17.33203125" collapsed="true"/>
@@ -8208,10 +8211,10 @@
       <c r="AH1" s="3"/>
     </row>
     <row ht="72" r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1006</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -8308,10 +8311,10 @@
       <c r="AH2" s="4"/>
     </row>
     <row ht="72" r="3" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1007</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -8413,7 +8416,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5776B0E-DB55-4350-9FD4-A6F4560407FB}">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -8518,10 +8521,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1039</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -8615,10 +8618,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1040</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -8718,7 +8721,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DAED720-8B00-473F-B284-AD53190F508A}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -8811,10 +8814,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1035</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -8898,10 +8901,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1036</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -8991,7 +8994,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1473DEC-6EE5-4076-9D5F-5EF76D644876}">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -9096,10 +9099,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1037</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -9193,10 +9196,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1038</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -9296,7 +9299,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A2BFFF-8CE2-4286-9146-DB049A020FA4}">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -9392,10 +9395,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1033</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -9480,10 +9483,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1034</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -9574,7 +9577,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD943804-0444-45BD-878A-2DB8B5C8234B}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -9667,10 +9670,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1025</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -9748,10 +9751,10 @@
       <c r="AC2" s="2"/>
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1026</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -9835,7 +9838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2598D2-608A-4EC2-A59A-28A4F2F2C19C}">
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:32" x14ac:dyDescent="0.3">
@@ -9937,10 +9940,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1091</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -10033,10 +10036,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1092</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -10135,7 +10138,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C6E4E3-FEB0-4C8B-8567-D979A0CFEDEF}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -10225,10 +10228,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1027</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -10305,10 +10308,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1028</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -10391,7 +10394,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE49C93-4BD2-4356-A28C-773B8D671B0F}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -10490,10 +10493,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1029</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -10579,10 +10582,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1030</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -10674,7 +10677,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0FF61A-DB8D-4A74-B78B-03F8F9F8B349}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -10773,10 +10776,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1031</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -10862,10 +10865,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1032</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -10957,7 +10960,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BB3CFB-F620-4173-A70F-13BA05E908A1}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -11047,10 +11050,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1050</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11129,10 +11132,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1051</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11217,7 +11220,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D02957-4C1C-4B36-8539-E094F8816C63}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -11307,10 +11310,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1048</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11389,10 +11392,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1049</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11477,7 +11480,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB69706-E238-4434-A63F-310C1977C6F0}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -11576,10 +11579,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1052</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11667,10 +11670,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1053</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11764,7 +11767,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3025D6A-7D6F-4C6F-96B5-791B34BCC219}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -11854,10 +11857,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1058</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11936,10 +11939,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1059</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12024,7 +12027,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C87FB397-5204-4FE3-B53C-72270511A532}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -12114,10 +12117,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1056</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -12196,10 +12199,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1057</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12284,7 +12287,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D49FB132-06F3-42B4-B1F9-A19038A385CE}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -12383,10 +12386,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1062</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -12474,10 +12477,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1063</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12571,7 +12574,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E72A2B1-158A-4CBE-92BF-97BEEB618388}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -12670,10 +12673,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1060</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -12761,10 +12764,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1061</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12858,7 +12861,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" style="2" width="8.6640625" collapsed="true"/>
@@ -12954,11 +12957,11 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
-        <v>1087</v>
+      <c r="B2" t="s" s="2">
+        <v>1094</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -13041,10 +13044,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="2">
         <v>1088</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -13137,7 +13140,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F49C59E-95FC-4A4C-AF9C-FF331A4E9E2C}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -13227,10 +13230,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1043</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -13309,10 +13312,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>629</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -13397,7 +13400,7 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C0AE3F5-1EA2-4637-B154-6C76E01F26D3}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -13487,10 +13490,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1041</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -13569,10 +13572,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1042</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -13657,7 +13660,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD921781-5791-4926-9100-5C0AAE19E7EB}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -13756,10 +13759,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1044</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -13847,10 +13850,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1045</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -13944,7 +13947,7 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2214AEC-363E-46E4-BBEE-32CDF3D3A6A4}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -14043,10 +14046,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1046</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -14134,10 +14137,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1047</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -14231,7 +14234,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{635B70C7-5F0C-49BF-B62E-2D9C67AF607B}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -14330,10 +14333,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1054</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -14421,10 +14424,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1055</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -14518,7 +14521,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA69CD0F-BD47-4004-A91B-17A22C7F7735}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" style="2" width="8.88671875" collapsed="true"/>
@@ -14617,10 +14620,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="2">
         <v>1093</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -14697,10 +14700,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="2">
         <v>863</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -14783,7 +14786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EF7E36-4F46-42AF-81C0-1EDDD67C9FDF}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -14873,10 +14876,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1079</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -14953,10 +14956,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1080</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -15039,7 +15042,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6359DCBA-59FF-4F94-BFD9-D794DEE8EC36}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -15138,10 +15141,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1081</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -15227,10 +15230,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1082</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -15322,7 +15325,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAEEA5C-DCE4-437D-991D-54A142ED2AFD}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -15421,10 +15424,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1083</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -15510,10 +15513,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1084</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -15605,7 +15608,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59C18C8-BC16-4EF9-ABC9-D44DBC5FD391}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -15695,10 +15698,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1064</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -15751,10 +15754,10 @@
       <c r="AB2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1065</v>
       </c>
       <c r="C3" s="1" t="s">
